--- a/docs/Class-D.xlsx
+++ b/docs/Class-D.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Class-D\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF12FCB-7FB2-4F8E-B447-B7FFF41A7B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5623D3A-60C3-4061-8078-B8331A909215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB設計" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="65">
   <si>
     <t>テーブル名：login_page</t>
   </si>
@@ -142,13 +145,91 @@
   </si>
   <si>
     <t>リプライ日時</t>
+  </si>
+  <si>
+    <t>CREATE TABLE login_page (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_id    VARCHAR2(20)  CONSTRAINT pk_login_page PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    password   VARCHAR2(50)  CONSTRAINT nn_login_password NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_name  VARCHAR2(50)</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <t>CREATE TABLE cloudy_thread (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_id     NUMBER(6)      CONSTRAINT pk_cloudy_thread PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_text   VARCHAR2(200)  CONSTRAINT nn_thread_text NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_tag    VARCHAR2(80),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_date   DATE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_likes  NUMBER(4),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_count  NUMBER(3),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_id   VARCHAR2(20),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONSTRAINT fk_thread_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        FOREIGN KEY (user_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        REFERENCES login_page (user_id)</t>
+  </si>
+  <si>
+    <t>CREATE TABLE cloudy_reply (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    re_id    NUMBER(6)       CONSTRAINT pk_cloudy_reply PRIMARY KEY,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    re_text  VARCHAR2(300)   CONSTRAINT nn_reply_text NOT NULL,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    re_date  DATE,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    th_id    NUMBER(6),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    user_id  VARCHAR2(20),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONSTRAINT fk_reply_thread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        FOREIGN KEY (th_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        REFERENCES cloudy_thread (th_id),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    CONSTRAINT fk_reply_user</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +239,15 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -204,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +312,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -525,9 +616,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -939,4 +1030,200 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E49E79A-C44B-4092-9A6E-194B7D1891F6}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="70.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3829D0B1-EB15-4AFB-8254-7B3EE66D4AFA}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="67.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F404809-F9A6-4D6E-9000-AF0DC2B340CD}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="66.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>